--- a/artfynd/A 31124-2024 artfynd.xlsx
+++ b/artfynd/A 31124-2024 artfynd.xlsx
@@ -9079,7 +9079,7 @@
         <v>136169728</v>
       </c>
       <c r="B68" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>136169737</v>
       </c>
       <c r="B69" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>136169748</v>
       </c>
       <c r="B70" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136169763</v>
       </c>
       <c r="B71" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>136169805</v>
       </c>
       <c r="B72" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>136169893</v>
       </c>
       <c r="B73" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>136169911</v>
       </c>
       <c r="B74" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136169951</v>
       </c>
       <c r="B75" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>136170009</v>
       </c>
       <c r="B76" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>136170039</v>
       </c>
       <c r="B77" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
